--- a/04_DESIGN_TABLES/DesignTable_5406.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5406.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -523,6 +523,21 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>SOCKAF@SOCKET</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SQAF@SQUARE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -769,7 +784,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -779,12 +794,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p013-t01: agrees on L2@DRIVE, C2HEX@HEX, TAPDRILL@BORE</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5406-08-04</t>
         </is>
       </c>
     </row>
@@ -821,7 +841,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -831,12 +851,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p013-t01: agrees on L2@DRIVE, C2HEX@HEX, TAPDRILL@BORE</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5406-08-06</t>
         </is>
       </c>
     </row>
@@ -2170,24 +2195,44 @@
           <t>5406-32-04</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.54</v>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>5406-32-04</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2-11 1/2 (male) x 1/4-18 (female) NPTF</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p13 table TFA-p013-t01 "5406 MP-FP REDUCER BUSHING" row 5406-32-04 col "L LGTH" = "1.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 446.2, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p13 5406 drawing: L = overall, C HEX = bushing hex (impact/F2b.json, certain); A1 DRILL is NOT a printed tap drill (likely only); same-table check on today's base: 30/31 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 5406-24-04 1.55 vs 1.57); C2HEX@HEX: Brennan TFA catalog p13 table TFA-p013-t01 "5406 MP-FP REDUCER BUSHING" row 5406-32-04 col "C HEX" = "2.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 446.2, page verified) [Brennan = yes 2026-10-18] - bushing hex; mapping: TFA p13 5406 drawing: L = overall, C HEX = bushing hex (impact/F2b.json, certain); A1 DRILL is NOT a printed tap drill (likely only); same-table check on today's base: 31/31 rows with an Air-Way/OMi value agree with this catalog column to rounding; TAPDRILL@BORE: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; the catalog A1 DRILL 0.431 is the male-end drill, not a printed tap drill (impact/F2b.json: likely only) - not used; THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (female end); THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD (male end); $PRP@Threads: thread texts from the part-number dashes, format of the built 5406 rows</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L2 / hex from the Brennan TFA catalog p13 alone; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2198,6 +2243,11 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>5406-32-04</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2392,24 +2442,32 @@
           <t>5406-HHP-08</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>0.61</v>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>5406-HHP-08</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF male plug (hollow hex)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p.67 table TFA-p067-t02 "5406-HP HOLLOW HEX PIPE PLUG" row 5406-HP-08 (= OMi 5406-HHP-08) col "L LGTH" = "0.610" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 251.0, page verified True) [Brennan = yes 2026-10-18] - overall length; SOCKAF@SOCKET: Brennan TFA catalog p.67 table TFA-p067-t02 "5406-HP HOLLOW HEX PIPE PLUG" row 5406-HP-08 (= OMi 5406-HHP-08) col "C HEX" = "0.375" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 251.0, page verified True) [Brennan = yes 2026-10-18] - socket across flats [column not in today's base table: add it]; $PRP@Threads: Brennan TFA catalog p.67 table TFA-p067-t02 "5406-HP HOLLOW HEX PIPE PLUG" row 5406-HP-08 col "A1 NPTF" = "1/2-14" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 251.0, page verified True) [Brennan = yes 2026-10-18] (thread callout)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2421,6 +2479,14 @@
         <is>
           <t>5406-HHP-08</t>
         </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="41">
@@ -2688,24 +2754,32 @@
           <t>5406-SHP-08</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>1.02</v>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>5406-SHP-08</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF male plug (square head)</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p.67 table TFA-p067-t04 "5406-SHP SQUARE HEAD PIPE PLUG" row 5406-SHP-08 (= OMi 5406-SHP-08) col "L LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 188.9, page verified True) [Brennan = yes 2026-10-18] - overall length incl. the head; SQAF@SQUARE: Brennan TFA catalog p.67 table TFA-p067-t04 "5406-SHP SQUARE HEAD PIPE PLUG" row 5406-SHP-08 (= OMi 5406-SHP-08) col "Y FLATS" = "0.563" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 188.9, page verified True) [Brennan = yes 2026-10-18] - square across flats [column not in today's base table: add it]; $PRP@Threads: Brennan TFA catalog p.67 table TFA-p067-t04 "5406-SHP SQUARE HEAD PIPE PLUG" row 5406-SHP-08 col "A1 NPTF" = "1/2-14" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 188.9, page verified True) [Brennan = yes 2026-10-18] (thread callout)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2717,6 +2791,14 @@
         <is>
           <t>5406-SHP-08</t>
         </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="49">
